--- a/source/Hoyeh Menu Latest Updated.xlsx
+++ b/source/Hoyeh Menu Latest Updated.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Pictures\Hoyeh\source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rws\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1798B815-4344-4C6A-9FFA-D0404621104A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9272781-331F-4A4C-8707-D1AF8A1C1C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="532">
   <si>
     <t>Meal</t>
   </si>
@@ -1687,6 +1687,9 @@
   </si>
   <si>
     <t>Luncheon Meat 午餐肉</t>
+  </si>
+  <si>
+    <t>4 x Salads (Caesar and Vinaigrette)</t>
   </si>
 </sst>
 </file>
@@ -2475,57 +2478,63 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2538,9 +2547,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2548,9 +2554,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2888,30 +2891,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3331950C-5F09-41DF-8A79-5F2EED696A70}">
   <dimension ref="A1:J83"/>
-  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.44140625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="47.77734375" style="15" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.453125" style="15" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="75"/>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="77"/>
-    </row>
-    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="78" t="s">
+    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+      <c r="A1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="76"/>
+    </row>
+    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="79"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2934,9 +2937,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
       <c r="C3" s="3">
         <v>46083</v>
       </c>
@@ -2959,8 +2962,8 @@
         <v>46089</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="82" t="s">
+    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="81" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="23" t="s">
@@ -2988,8 +2991,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="83"/>
+    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="82"/>
       <c r="B5" s="25" t="s">
         <v>9</v>
       </c>
@@ -3015,8 +3018,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="83"/>
+    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="82"/>
       <c r="B6" s="27" t="s">
         <v>10</v>
       </c>
@@ -3042,8 +3045,8 @@
         <v>363</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="83"/>
+    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="82"/>
       <c r="B7" s="25" t="s">
         <v>23</v>
       </c>
@@ -3069,8 +3072,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84"/>
+    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="83"/>
       <c r="B8" s="30" t="s">
         <v>11</v>
       </c>
@@ -3096,8 +3099,8 @@
         <v>306</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="85" t="s">
+    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="84" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="24" t="s">
@@ -3125,8 +3128,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
+    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="85"/>
       <c r="B10" s="18" t="s">
         <v>50</v>
       </c>
@@ -3152,9 +3155,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="72" t="s">
+    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="85"/>
+      <c r="B11" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="20" t="s">
@@ -3179,9 +3182,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="73"/>
+    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="85"/>
+      <c r="B12" s="88"/>
       <c r="C12" s="20" t="s">
         <v>312</v>
       </c>
@@ -3204,9 +3207,9 @@
         <v>269</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="73"/>
+    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="85"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="20" t="s">
         <v>317</v>
       </c>
@@ -3229,9 +3232,9 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="73"/>
+    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="85"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="20" t="s">
         <v>101</v>
       </c>
@@ -3254,9 +3257,9 @@
         <v>323</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="73"/>
+    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="85"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="20" t="s">
         <v>62</v>
       </c>
@@ -3279,9 +3282,9 @@
         <v>324</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="88"/>
+    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="85"/>
+      <c r="B16" s="89"/>
       <c r="C16" s="20" t="s">
         <v>28</v>
       </c>
@@ -3304,8 +3307,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
+    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="85"/>
       <c r="B17" s="18" t="s">
         <v>70</v>
       </c>
@@ -3331,8 +3334,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="85"/>
       <c r="B18" s="18" t="s">
         <v>13</v>
       </c>
@@ -3358,8 +3361,8 @@
         <v>330</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="87"/>
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="86"/>
       <c r="B19" s="39" t="s">
         <v>71</v>
       </c>
@@ -3385,8 +3388,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="89" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="91" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="33" t="s">
@@ -3414,8 +3417,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="91"/>
       <c r="B21" s="18" t="s">
         <v>50</v>
       </c>
@@ -3441,9 +3444,9 @@
         <v>339</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="89"/>
-      <c r="B22" s="72" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="91"/>
+      <c r="B22" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="32" t="s">
@@ -3468,9 +3471,9 @@
         <v>219</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
-      <c r="B23" s="73"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="91"/>
+      <c r="B23" s="88"/>
       <c r="C23" s="32" t="s">
         <v>89</v>
       </c>
@@ -3493,9 +3496,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
-      <c r="B24" s="73"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="91"/>
+      <c r="B24" s="88"/>
       <c r="C24" s="32" t="s">
         <v>93</v>
       </c>
@@ -3518,9 +3521,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="89"/>
-      <c r="B25" s="73"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="91"/>
+      <c r="B25" s="88"/>
       <c r="C25" s="20" t="s">
         <v>349</v>
       </c>
@@ -3543,9 +3546,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="89"/>
-      <c r="B26" s="73"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="91"/>
+      <c r="B26" s="88"/>
       <c r="C26" s="20" t="s">
         <v>100</v>
       </c>
@@ -3568,9 +3571,9 @@
         <v>359</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="89"/>
-      <c r="B27" s="88"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="91"/>
+      <c r="B27" s="89"/>
       <c r="C27" s="20" t="s">
         <v>25</v>
       </c>
@@ -3593,8 +3596,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="91"/>
       <c r="B28" s="18" t="s">
         <v>70</v>
       </c>
@@ -3620,8 +3623,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="89"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="91"/>
       <c r="B29" s="18" t="s">
         <v>13</v>
       </c>
@@ -3647,8 +3650,8 @@
         <v>330</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="90"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="92"/>
       <c r="B30" s="39" t="s">
         <v>71</v>
       </c>
@@ -3674,8 +3677,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="91" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="93" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="24" t="s">
@@ -3703,8 +3706,8 @@
         <v>308</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="94"/>
       <c r="B32" s="18" t="s">
         <v>50</v>
       </c>
@@ -3730,9 +3733,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
-      <c r="B33" s="72" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="94"/>
+      <c r="B33" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C33" s="20" t="s">
@@ -3757,9 +3760,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92"/>
-      <c r="B34" s="73"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="20" t="s">
         <v>312</v>
       </c>
@@ -3782,9 +3785,9 @@
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="92"/>
-      <c r="B35" s="73"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="20" t="s">
         <v>317</v>
       </c>
@@ -3807,9 +3810,9 @@
         <v>314</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="92"/>
-      <c r="B36" s="73"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="88"/>
       <c r="C36" s="20" t="s">
         <v>101</v>
       </c>
@@ -3832,9 +3835,9 @@
         <v>323</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="92"/>
-      <c r="B37" s="73"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="94"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="20" t="s">
         <v>62</v>
       </c>
@@ -3857,8 +3860,8 @@
         <v>324</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="92"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="94"/>
       <c r="B38" s="18" t="s">
         <v>70</v>
       </c>
@@ -3884,8 +3887,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="92"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="94"/>
       <c r="B39" s="18" t="s">
         <v>13</v>
       </c>
@@ -3911,8 +3914,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="92"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="94"/>
       <c r="B40" s="18" t="s">
         <v>71</v>
       </c>
@@ -3938,7 +3941,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="46" t="s">
         <v>14</v>
       </c>
@@ -3967,13 +3970,13 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="9"/>
       <c r="E42" s="10"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="11"/>
@@ -3984,7 +3987,7 @@
       <c r="H43" s="12"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="11"/>
@@ -3995,15 +3998,15 @@
       <c r="H44" s="12"/>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="6"/>
@@ -4014,7 +4017,7 @@
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="8"/>
@@ -4025,7 +4028,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="8"/>
@@ -4036,7 +4039,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="11"/>
@@ -4047,7 +4050,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="11"/>
@@ -4058,12 +4061,12 @@
       <c r="H51" s="12"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="G52" s="10"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="11"/>
@@ -4074,15 +4077,15 @@
       <c r="H53" s="12"/>
       <c r="I53" s="6"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="6"/>
@@ -4093,27 +4096,27 @@
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="G60" s="8"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="11"/>
@@ -4124,7 +4127,7 @@
       <c r="H61" s="12"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="11"/>
@@ -4135,15 +4138,15 @@
       <c r="H62" s="12"/>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="11"/>
@@ -4154,7 +4157,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="11"/>
@@ -4165,7 +4168,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="11"/>
@@ -4176,7 +4179,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="11"/>
@@ -4187,7 +4190,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="11"/>
@@ -4198,7 +4201,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="11"/>
@@ -4209,7 +4212,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="11"/>
@@ -4220,7 +4223,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="11"/>
@@ -4231,7 +4234,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="11"/>
@@ -4242,7 +4245,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -4253,7 +4256,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="6"/>
@@ -4264,30 +4267,30 @@
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="74"/>
-      <c r="H76" s="74"/>
-      <c r="I76" s="74"/>
-    </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="73"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="73"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="73"/>
+      <c r="I76" s="73"/>
+    </row>
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
-      <c r="C77" s="74"/>
-      <c r="D77" s="74"/>
-      <c r="E77" s="74"/>
-      <c r="F77" s="74"/>
-      <c r="G77" s="74"/>
-      <c r="H77" s="74"/>
-      <c r="I77" s="74"/>
-      <c r="J77" s="74"/>
-    </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="73"/>
+      <c r="D77" s="73"/>
+      <c r="E77" s="73"/>
+      <c r="F77" s="73"/>
+      <c r="G77" s="73"/>
+      <c r="H77" s="73"/>
+      <c r="I77" s="73"/>
+      <c r="J77" s="73"/>
+    </row>
+    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -4298,7 +4301,7 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="6"/>
@@ -4309,19 +4312,19 @@
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="16"/>
       <c r="B83" s="16"/>
     </row>
@@ -4349,30 +4352,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF35105-E78C-446D-B499-ECA475F17C6E}">
   <dimension ref="A1:J82"/>
-  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.44140625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="47.77734375" style="15" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.453125" style="15" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="75"/>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="77"/>
-    </row>
-    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="78" t="s">
+    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+      <c r="A1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="76"/>
+    </row>
+    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="79"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4395,9 +4398,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
       <c r="C3" s="3">
         <v>46090</v>
       </c>
@@ -4420,8 +4423,8 @@
         <v>46096</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="82" t="s">
+    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="81" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="50" t="s">
@@ -4449,12 +4452,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="83"/>
+    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="82"/>
       <c r="B5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="72" t="s">
         <v>512</v>
       </c>
       <c r="D5" s="26" t="s">
@@ -4476,8 +4479,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="83"/>
+    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="82"/>
       <c r="B6" s="52" t="s">
         <v>10</v>
       </c>
@@ -4503,8 +4506,8 @@
         <v>364</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="83"/>
+    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="82"/>
       <c r="B7" s="51" t="s">
         <v>23</v>
       </c>
@@ -4530,8 +4533,8 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84"/>
+    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="83"/>
       <c r="B8" s="53" t="s">
         <v>11</v>
       </c>
@@ -4557,8 +4560,8 @@
         <v>366</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="85" t="s">
+    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="84" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="24" t="s">
@@ -4586,8 +4589,8 @@
         <v>371</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
+    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="85"/>
       <c r="B10" s="18" t="s">
         <v>50</v>
       </c>
@@ -4613,9 +4616,9 @@
         <v>368</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="72" t="s">
+    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="85"/>
+      <c r="B11" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="20" t="s">
@@ -4640,9 +4643,9 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="73"/>
+    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="85"/>
+      <c r="B12" s="88"/>
       <c r="C12" s="20" t="s">
         <v>515</v>
       </c>
@@ -4665,9 +4668,9 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="73"/>
+    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="85"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="20" t="s">
         <v>516</v>
       </c>
@@ -4690,9 +4693,9 @@
         <v>381</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="73"/>
+    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="85"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="20" t="s">
         <v>517</v>
       </c>
@@ -4715,9 +4718,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="73"/>
+    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="85"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="20" t="s">
         <v>518</v>
       </c>
@@ -4740,9 +4743,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="88"/>
+    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="85"/>
+      <c r="B16" s="89"/>
       <c r="C16" s="20" t="s">
         <v>519</v>
       </c>
@@ -4765,8 +4768,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
+    <row r="17" spans="1:9" ht="94" x14ac:dyDescent="0.35">
+      <c r="A17" s="85"/>
       <c r="B17" s="18" t="s">
         <v>70</v>
       </c>
@@ -4774,7 +4777,7 @@
         <v>520</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="E17" s="18" t="s">
         <v>74</v>
@@ -4792,8 +4795,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="85"/>
       <c r="B18" s="18" t="s">
         <v>13</v>
       </c>
@@ -4819,8 +4822,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="87"/>
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="86"/>
       <c r="B19" s="39" t="s">
         <v>71</v>
       </c>
@@ -4846,8 +4849,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="93" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="90" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="24" t="s">
@@ -4875,8 +4878,8 @@
         <v>375</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="91"/>
       <c r="B21" s="18" t="s">
         <v>50</v>
       </c>
@@ -4902,9 +4905,9 @@
         <v>387</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="89"/>
-      <c r="B22" s="72" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="91"/>
+      <c r="B22" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="20" t="s">
@@ -4929,9 +4932,9 @@
         <v>232</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
-      <c r="B23" s="73"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="91"/>
+      <c r="B23" s="88"/>
       <c r="C23" s="20" t="s">
         <v>526</v>
       </c>
@@ -4954,9 +4957,9 @@
         <v>403</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
-      <c r="B24" s="73"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="91"/>
+      <c r="B24" s="88"/>
       <c r="C24" s="20" t="s">
         <v>527</v>
       </c>
@@ -4979,9 +4982,9 @@
         <v>395</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="89"/>
-      <c r="B25" s="73"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="91"/>
+      <c r="B25" s="88"/>
       <c r="C25" s="20" t="s">
         <v>528</v>
       </c>
@@ -5004,9 +5007,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="89"/>
-      <c r="B26" s="73"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="91"/>
+      <c r="B26" s="88"/>
       <c r="C26" s="20" t="s">
         <v>529</v>
       </c>
@@ -5029,9 +5032,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="89"/>
-      <c r="B27" s="88"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="91"/>
+      <c r="B27" s="89"/>
       <c r="C27" s="20" t="s">
         <v>530</v>
       </c>
@@ -5054,8 +5057,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="94" x14ac:dyDescent="0.35">
+      <c r="A28" s="91"/>
       <c r="B28" s="18" t="s">
         <v>70</v>
       </c>
@@ -5063,7 +5066,7 @@
         <v>520</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="E28" s="18" t="s">
         <v>74</v>
@@ -5081,8 +5084,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="89"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="91"/>
       <c r="B29" s="18" t="s">
         <v>13</v>
       </c>
@@ -5108,8 +5111,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="90"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="92"/>
       <c r="B30" s="39" t="s">
         <v>71</v>
       </c>
@@ -5135,8 +5138,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="91" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="93" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="24" t="s">
@@ -5164,8 +5167,8 @@
         <v>371</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="94"/>
       <c r="B32" s="18" t="s">
         <v>50</v>
       </c>
@@ -5191,9 +5194,9 @@
         <v>368</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
-      <c r="B33" s="72" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="94"/>
+      <c r="B33" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C33" s="20" t="s">
@@ -5218,9 +5221,9 @@
         <v>229</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92"/>
-      <c r="B34" s="73"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="20" t="s">
         <v>515</v>
       </c>
@@ -5243,9 +5246,9 @@
         <v>261</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="92"/>
-      <c r="B35" s="73"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="20" t="s">
         <v>517</v>
       </c>
@@ -5268,9 +5271,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="92"/>
-      <c r="B36" s="73"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="88"/>
       <c r="C36" s="20" t="s">
         <v>518</v>
       </c>
@@ -5293,9 +5296,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="92"/>
-      <c r="B37" s="73"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="94"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="20" t="s">
         <v>519</v>
       </c>
@@ -5318,8 +5321,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="92"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="94"/>
       <c r="B38" s="18" t="s">
         <v>70</v>
       </c>
@@ -5327,7 +5330,7 @@
         <v>520</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>74</v>
@@ -5345,8 +5348,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="92"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="94"/>
       <c r="B39" s="18" t="s">
         <v>13</v>
       </c>
@@ -5372,8 +5375,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="92"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="94"/>
       <c r="B40" s="18" t="s">
         <v>71</v>
       </c>
@@ -5399,7 +5402,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="46" t="s">
         <v>14</v>
       </c>
@@ -5428,7 +5431,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="11"/>
@@ -5439,7 +5442,7 @@
       <c r="H42" s="12"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="11"/>
@@ -5450,15 +5453,15 @@
       <c r="H43" s="12"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
@@ -5469,7 +5472,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -5480,7 +5483,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="8"/>
@@ -5491,7 +5494,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="11"/>
@@ -5502,7 +5505,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="11"/>
@@ -5513,12 +5516,12 @@
       <c r="H50" s="12"/>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="G51" s="10"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="11"/>
@@ -5529,15 +5532,15 @@
       <c r="H52" s="12"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -5548,27 +5551,27 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="11"/>
@@ -5579,7 +5582,7 @@
       <c r="H60" s="12"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="11"/>
@@ -5590,15 +5593,15 @@
       <c r="H61" s="12"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="11"/>
@@ -5609,7 +5612,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="11"/>
@@ -5620,7 +5623,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="11"/>
@@ -5631,7 +5634,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="11"/>
@@ -5642,7 +5645,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="11"/>
@@ -5653,7 +5656,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="11"/>
@@ -5664,7 +5667,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="11"/>
@@ -5675,7 +5678,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="11"/>
@@ -5686,7 +5689,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="11"/>
@@ -5697,7 +5700,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -5708,7 +5711,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -5719,30 +5722,30 @@
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="74"/>
-      <c r="I75" s="74"/>
-    </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="73"/>
+      <c r="D75" s="73"/>
+      <c r="E75" s="73"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="73"/>
+      <c r="H75" s="73"/>
+      <c r="I75" s="73"/>
+    </row>
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="74"/>
-      <c r="H76" s="74"/>
-      <c r="I76" s="74"/>
-      <c r="J76" s="74"/>
-    </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="73"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="73"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="73"/>
+      <c r="I76" s="73"/>
+      <c r="J76" s="73"/>
+    </row>
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -5753,7 +5756,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -5764,19 +5767,19 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="16"/>
       <c r="B82" s="16"/>
     </row>
@@ -5804,30 +5807,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADFDDF52-516B-4631-A9D2-1246E2DB53C6}">
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.44140625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="47.77734375" style="15" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.453125" style="15" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="75"/>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="77"/>
-    </row>
-    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="78" t="s">
+    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+      <c r="A1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="76"/>
+    </row>
+    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="79"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5850,9 +5853,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
       <c r="C3" s="3">
         <v>46097</v>
       </c>
@@ -5875,8 +5878,8 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="82" t="s">
+    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="81" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="50" t="s">
@@ -5904,8 +5907,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="83"/>
+    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="82"/>
       <c r="B5" s="51" t="s">
         <v>9</v>
       </c>
@@ -5931,8 +5934,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="83"/>
+    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="82"/>
       <c r="B6" s="52" t="s">
         <v>10</v>
       </c>
@@ -5958,8 +5961,8 @@
         <v>362</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="83"/>
+    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="82"/>
       <c r="B7" s="51" t="s">
         <v>23</v>
       </c>
@@ -5985,8 +5988,8 @@
         <v>407</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84"/>
+    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="83"/>
       <c r="B8" s="53" t="s">
         <v>11</v>
       </c>
@@ -6012,8 +6015,8 @@
         <v>306</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="85" t="s">
+    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="84" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="24" t="s">
@@ -6041,8 +6044,8 @@
         <v>416</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
+    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="85"/>
       <c r="B10" s="18" t="s">
         <v>50</v>
       </c>
@@ -6068,9 +6071,9 @@
         <v>418</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="72" t="s">
+    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="85"/>
+      <c r="B11" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="32" t="s">
@@ -6095,9 +6098,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="73"/>
+    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="85"/>
+      <c r="B12" s="88"/>
       <c r="C12" s="32" t="s">
         <v>413</v>
       </c>
@@ -6120,9 +6123,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="73"/>
+    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="85"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="32" t="s">
         <v>420</v>
       </c>
@@ -6145,9 +6148,9 @@
         <v>430</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="73"/>
+    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="85"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="32" t="s">
         <v>431</v>
       </c>
@@ -6170,9 +6173,9 @@
         <v>432</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="73"/>
+    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="85"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="32" t="s">
         <v>436</v>
       </c>
@@ -6195,9 +6198,9 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="88"/>
+    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="85"/>
+      <c r="B16" s="89"/>
       <c r="C16" s="32" t="s">
         <v>161</v>
       </c>
@@ -6220,8 +6223,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
+    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="85"/>
       <c r="B17" s="18" t="s">
         <v>70</v>
       </c>
@@ -6247,8 +6250,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="85"/>
       <c r="B18" s="18" t="s">
         <v>13</v>
       </c>
@@ -6274,8 +6277,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="87"/>
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="86"/>
       <c r="B19" s="39" t="s">
         <v>71</v>
       </c>
@@ -6301,8 +6304,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="93" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="90" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="24" t="s">
@@ -6330,8 +6333,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="91"/>
       <c r="B21" s="18" t="s">
         <v>50</v>
       </c>
@@ -6357,9 +6360,9 @@
         <v>453</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="89"/>
-      <c r="B22" s="72" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="91"/>
+      <c r="B22" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="32" t="s">
@@ -6384,9 +6387,9 @@
         <v>238</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
-      <c r="B23" s="73"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="91"/>
+      <c r="B23" s="88"/>
       <c r="C23" s="32" t="s">
         <v>167</v>
       </c>
@@ -6409,9 +6412,9 @@
         <v>275</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
-      <c r="B24" s="73"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="91"/>
+      <c r="B24" s="88"/>
       <c r="C24" s="32" t="s">
         <v>59</v>
       </c>
@@ -6434,9 +6437,9 @@
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="89"/>
-      <c r="B25" s="73"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="91"/>
+      <c r="B25" s="88"/>
       <c r="C25" s="32" t="s">
         <v>458</v>
       </c>
@@ -6459,9 +6462,9 @@
         <v>463</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="89"/>
-      <c r="B26" s="73"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="91"/>
+      <c r="B26" s="88"/>
       <c r="C26" s="32" t="s">
         <v>62</v>
       </c>
@@ -6484,9 +6487,9 @@
         <v>462</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="89"/>
-      <c r="B27" s="88"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="91"/>
+      <c r="B27" s="89"/>
       <c r="C27" s="32" t="s">
         <v>407</v>
       </c>
@@ -6509,8 +6512,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="91"/>
       <c r="B28" s="18" t="s">
         <v>70</v>
       </c>
@@ -6536,8 +6539,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="89"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="91"/>
       <c r="B29" s="18" t="s">
         <v>13</v>
       </c>
@@ -6563,8 +6566,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="90"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="92"/>
       <c r="B30" s="39" t="s">
         <v>71</v>
       </c>
@@ -6590,8 +6593,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="91" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="93" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="24" t="s">
@@ -6619,8 +6622,8 @@
         <v>416</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="94"/>
       <c r="B32" s="18" t="s">
         <v>50</v>
       </c>
@@ -6646,9 +6649,9 @@
         <v>418</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
-      <c r="B33" s="72" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="94"/>
+      <c r="B33" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C33" s="32" t="s">
@@ -6673,9 +6676,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92"/>
-      <c r="B34" s="73"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="32" t="s">
         <v>413</v>
       </c>
@@ -6698,9 +6701,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="92"/>
-      <c r="B35" s="73"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="32" t="s">
         <v>431</v>
       </c>
@@ -6723,9 +6726,9 @@
         <v>432</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="92"/>
-      <c r="B36" s="73"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="88"/>
       <c r="C36" s="32" t="s">
         <v>436</v>
       </c>
@@ -6748,9 +6751,9 @@
         <v>433</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="92"/>
-      <c r="B37" s="73"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="94"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="32" t="s">
         <v>161</v>
       </c>
@@ -6773,8 +6776,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="92"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="94"/>
       <c r="B38" s="18" t="s">
         <v>70</v>
       </c>
@@ -6800,8 +6803,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="92"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="94"/>
       <c r="B39" s="18" t="s">
         <v>13</v>
       </c>
@@ -6827,8 +6830,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="92"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="94"/>
       <c r="B40" s="18" t="s">
         <v>71</v>
       </c>
@@ -6854,7 +6857,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="150.44999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="150.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="46" t="s">
         <v>14</v>
       </c>
@@ -6883,7 +6886,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="11"/>
@@ -6894,15 +6897,15 @@
       <c r="H42" s="12"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -6913,7 +6916,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="8"/>
@@ -6924,7 +6927,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -6935,7 +6938,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="11"/>
@@ -6946,7 +6949,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="11"/>
@@ -6957,12 +6960,12 @@
       <c r="H49" s="12"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="G50" s="10"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="11"/>
@@ -6973,15 +6976,15 @@
       <c r="H51" s="12"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -6992,27 +6995,27 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="11"/>
@@ -7023,7 +7026,7 @@
       <c r="H59" s="12"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="11"/>
@@ -7034,15 +7037,15 @@
       <c r="H60" s="12"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="11"/>
@@ -7053,7 +7056,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="11"/>
@@ -7064,7 +7067,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="11"/>
@@ -7075,7 +7078,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="11"/>
@@ -7086,7 +7089,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="11"/>
@@ -7097,7 +7100,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="11"/>
@@ -7108,7 +7111,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="11"/>
@@ -7119,7 +7122,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="11"/>
@@ -7130,7 +7133,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="11"/>
@@ -7141,7 +7144,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -7152,7 +7155,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -7163,30 +7166,30 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="74"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="74"/>
-      <c r="H74" s="74"/>
-      <c r="I74" s="74"/>
-    </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="73"/>
+      <c r="D74" s="73"/>
+      <c r="E74" s="73"/>
+      <c r="F74" s="73"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="73"/>
+      <c r="I74" s="73"/>
+    </row>
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="74"/>
-      <c r="I75" s="74"/>
-      <c r="J75" s="74"/>
-    </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="73"/>
+      <c r="D75" s="73"/>
+      <c r="E75" s="73"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="73"/>
+      <c r="H75" s="73"/>
+      <c r="I75" s="73"/>
+      <c r="J75" s="73"/>
+    </row>
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -7197,7 +7200,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -7208,19 +7211,19 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="16"/>
       <c r="B81" s="16"/>
     </row>
@@ -7248,30 +7251,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29988196-DFEB-46AE-A95C-9191B0B4EB55}">
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.44140625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="47.77734375" style="15" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.453125" style="15" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="75"/>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="77"/>
-    </row>
-    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="78" t="s">
+    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+      <c r="A1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="76"/>
+    </row>
+    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="79"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7294,9 +7297,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
       <c r="C3" s="3">
         <v>46104</v>
       </c>
@@ -7319,8 +7322,8 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="82" t="s">
+    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="81" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="50" t="s">
@@ -7348,8 +7351,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="83"/>
+    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="82"/>
       <c r="B5" s="51" t="s">
         <v>9</v>
       </c>
@@ -7375,8 +7378,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="83"/>
+    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="82"/>
       <c r="B6" s="52" t="s">
         <v>10</v>
       </c>
@@ -7402,8 +7405,8 @@
         <v>467</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="83"/>
+    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="82"/>
       <c r="B7" s="51" t="s">
         <v>23</v>
       </c>
@@ -7429,8 +7432,8 @@
         <v>468</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84"/>
+    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="83"/>
       <c r="B8" s="53" t="s">
         <v>11</v>
       </c>
@@ -7456,8 +7459,8 @@
         <v>469</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="85" t="s">
+    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="84" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="68" t="s">
@@ -7485,8 +7488,8 @@
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
+    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="85"/>
       <c r="B10" s="69" t="s">
         <v>50</v>
       </c>
@@ -7512,9 +7515,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="94" t="s">
+    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="85"/>
+      <c r="B11" s="95" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="20" t="s">
@@ -7539,9 +7542,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="95"/>
+    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="85"/>
+      <c r="B12" s="96"/>
       <c r="C12" s="20" t="s">
         <v>191</v>
       </c>
@@ -7564,9 +7567,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="95"/>
+    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="85"/>
+      <c r="B13" s="96"/>
       <c r="C13" s="20" t="s">
         <v>481</v>
       </c>
@@ -7589,9 +7592,9 @@
         <v>454</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="95"/>
+    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="85"/>
+      <c r="B14" s="96"/>
       <c r="C14" s="20" t="s">
         <v>277</v>
       </c>
@@ -7614,9 +7617,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="95"/>
+    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="85"/>
+      <c r="B15" s="96"/>
       <c r="C15" s="20" t="s">
         <v>276</v>
       </c>
@@ -7639,9 +7642,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="96"/>
+    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="85"/>
+      <c r="B16" s="97"/>
       <c r="C16" s="20" t="s">
         <v>175</v>
       </c>
@@ -7664,8 +7667,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
+    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="85"/>
       <c r="B17" s="69" t="s">
         <v>70</v>
       </c>
@@ -7691,8 +7694,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="85"/>
       <c r="B18" s="69" t="s">
         <v>13</v>
       </c>
@@ -7718,8 +7721,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="87"/>
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="86"/>
       <c r="B19" s="70" t="s">
         <v>71</v>
       </c>
@@ -7745,8 +7748,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="93" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="90" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="68" t="s">
@@ -7774,8 +7777,8 @@
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="91"/>
       <c r="B21" s="69" t="s">
         <v>50</v>
       </c>
@@ -7801,9 +7804,9 @@
         <v>273</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="89"/>
-      <c r="B22" s="94" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="91"/>
+      <c r="B22" s="95" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="20" t="s">
@@ -7828,9 +7831,9 @@
         <v>298</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
-      <c r="B23" s="95"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="91"/>
+      <c r="B23" s="96"/>
       <c r="C23" s="20" t="s">
         <v>200</v>
       </c>
@@ -7853,9 +7856,9 @@
         <v>203</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
-      <c r="B24" s="95"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="91"/>
+      <c r="B24" s="96"/>
       <c r="C24" s="20" t="s">
         <v>204</v>
       </c>
@@ -7878,9 +7881,9 @@
         <v>499</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="89"/>
-      <c r="B25" s="95"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="91"/>
+      <c r="B25" s="96"/>
       <c r="C25" s="20" t="s">
         <v>124</v>
       </c>
@@ -7903,9 +7906,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="89"/>
-      <c r="B26" s="95"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="91"/>
+      <c r="B26" s="96"/>
       <c r="C26" s="20" t="s">
         <v>288</v>
       </c>
@@ -7928,9 +7931,9 @@
         <v>297</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="89"/>
-      <c r="B27" s="96"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="91"/>
+      <c r="B27" s="97"/>
       <c r="C27" s="20" t="s">
         <v>506</v>
       </c>
@@ -7953,8 +7956,8 @@
         <v>360</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="91"/>
       <c r="B28" s="69" t="s">
         <v>70</v>
       </c>
@@ -7980,8 +7983,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="89"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="91"/>
       <c r="B29" s="69" t="s">
         <v>13</v>
       </c>
@@ -8007,8 +8010,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="90"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="92"/>
       <c r="B30" s="70" t="s">
         <v>71</v>
       </c>
@@ -8034,8 +8037,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="91" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="93" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="24" t="s">
@@ -8063,8 +8066,8 @@
         <v>188</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="94"/>
       <c r="B32" s="18" t="s">
         <v>50</v>
       </c>
@@ -8090,9 +8093,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
-      <c r="B33" s="72" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="94"/>
+      <c r="B33" s="87" t="s">
         <v>48</v>
       </c>
       <c r="C33" s="20" t="s">
@@ -8117,9 +8120,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92"/>
-      <c r="B34" s="73"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="20" t="s">
         <v>191</v>
       </c>
@@ -8142,9 +8145,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="92"/>
-      <c r="B35" s="73"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="20" t="s">
         <v>277</v>
       </c>
@@ -8167,9 +8170,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="92"/>
-      <c r="B36" s="73"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="88"/>
       <c r="C36" s="20" t="s">
         <v>276</v>
       </c>
@@ -8192,9 +8195,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="92"/>
-      <c r="B37" s="73"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="94"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="20" t="s">
         <v>175</v>
       </c>
@@ -8217,8 +8220,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="92"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="94"/>
       <c r="B38" s="18" t="s">
         <v>70</v>
       </c>
@@ -8244,8 +8247,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="92"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="94"/>
       <c r="B39" s="18" t="s">
         <v>13</v>
       </c>
@@ -8271,8 +8274,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="92"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="94"/>
       <c r="B40" s="18" t="s">
         <v>71</v>
       </c>
@@ -8298,7 +8301,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="119.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="119.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="46" t="s">
         <v>14</v>
       </c>
@@ -8327,7 +8330,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="11"/>
@@ -8338,15 +8341,15 @@
       <c r="H42" s="12"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -8357,7 +8360,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="8"/>
@@ -8368,7 +8371,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -8379,7 +8382,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="11"/>
@@ -8390,7 +8393,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="11"/>
@@ -8401,12 +8404,12 @@
       <c r="H49" s="12"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="G50" s="10"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="11"/>
@@ -8417,15 +8420,15 @@
       <c r="H51" s="12"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -8436,27 +8439,27 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="11"/>
@@ -8467,7 +8470,7 @@
       <c r="H59" s="12"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="11"/>
@@ -8478,15 +8481,15 @@
       <c r="H60" s="12"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="11"/>
@@ -8497,7 +8500,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="11"/>
@@ -8508,7 +8511,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="11"/>
@@ -8519,7 +8522,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="11"/>
@@ -8530,7 +8533,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="11"/>
@@ -8541,7 +8544,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="11"/>
@@ -8552,7 +8555,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="11"/>
@@ -8563,7 +8566,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="11"/>
@@ -8574,7 +8577,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="11"/>
@@ -8585,7 +8588,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -8596,7 +8599,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -8607,30 +8610,30 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="74"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="74"/>
-      <c r="H74" s="74"/>
-      <c r="I74" s="74"/>
-    </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="73"/>
+      <c r="D74" s="73"/>
+      <c r="E74" s="73"/>
+      <c r="F74" s="73"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="73"/>
+      <c r="I74" s="73"/>
+    </row>
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="74"/>
-      <c r="I75" s="74"/>
-      <c r="J75" s="74"/>
-    </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="73"/>
+      <c r="D75" s="73"/>
+      <c r="E75" s="73"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="73"/>
+      <c r="H75" s="73"/>
+      <c r="I75" s="73"/>
+      <c r="J75" s="73"/>
+    </row>
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -8641,7 +8644,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -8652,19 +8655,19 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="16"/>
       <c r="B81" s="16"/>
     </row>
